--- a/ComputationData.xlsx
+++ b/ComputationData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e41580a8ecfa9755/Documents/GitHub/LFSR-Research/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{332282E7-26CB-476A-93FC-FEF1924633F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="216" documentId="8_{332282E7-26CB-476A-93FC-FEF1924633F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41916249-7D20-436E-8F41-69616D7117E2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{1F3D20C0-FD03-43D0-AC57-8A2190F0F293}"/>
   </bookViews>
@@ -36,15 +36,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>Bits</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
   <si>
     <t>Sample Size</t>
   </si>
   <si>
     <t>Mean Time (secs)</t>
+  </si>
+  <si>
+    <t>% Change</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>O(n^2) (Berlekamp-Massey)</t>
+  </si>
+  <si>
+    <t>Tarter-Herasymov-Priebracha Algorithm</t>
+  </si>
+  <si>
+    <t>Berlekamp-Massey Algorithm</t>
+  </si>
+  <si>
+    <t># of Bits</t>
+  </si>
+  <si>
+    <t>Difference</t>
   </si>
 </sst>
 </file>
@@ -68,7 +86,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -87,7 +105,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -95,14 +113,157 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -118,6 +279,2443 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Seconds</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> of Computation Per 'n' Bits</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Tarter-Herasymov-Priebracha Algorithm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent1">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1000000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$I$2:$I$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1.3114539999999999E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.4442560000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.2838947199999996E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.947757348E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.38916964316000008</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.6873352859600006</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-15D6-4405-81E5-7CC17AD33C56}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$J$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Berlekamp-Massey Algorithm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent2">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent2">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1000000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$J$2:$J$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1.3114539999999999E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.3114539999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.3114539999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>131.1454</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>13114.539999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1311454</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-15D6-4405-81E5-7CC17AD33C56}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="969386047"/>
+        <c:axId val="969386527"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="969386047"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Bits</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+                <a:alpha val="10000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="969386527"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="969386527"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Seconds</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="969386047"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:dTable>
+        <c:showHorzBorder val="1"/>
+        <c:showVertBorder val="1"/>
+        <c:showOutline val="1"/>
+        <c:showKeys val="1"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+                <a:alpha val="54000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr rtl="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+      </c:dTable>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Difference Between Berlekamp-Massey</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> and THP</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$K$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Difference</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent1">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="95000"/>
+                          <a:alpha val="54000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1000000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$K$2:$K$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.26701144E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.30717010528</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>131.10592242651998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>13114.150830356839</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1311449.3126647139</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B554-49FB-9458-C80DEA5D8CF0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="961318207"/>
+        <c:axId val="961320127"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="961318207"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Bits</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+                <a:alpha val="10000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="961320127"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="961320127"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Seconds</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="961318207"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="233">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="233">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>3810</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>316785</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{875A8B95-DD85-E6B7-8EDF-7EE2A43E6615}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>16267</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>71362</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>524838</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>136132</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA965B0F-CAF6-5EBC-EBB3-3654AB6B307F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -437,38 +3035,328 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A34A7D4-8814-4566-A5FA-6FC1745EEF7A}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="2" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="24.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="1"/>
+    <col min="8" max="8" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="34.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.6640625" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="20" t="s">
         <v>2</v>
       </c>
+      <c r="E1" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <v>100</v>
+      </c>
+      <c r="B2" s="14">
+        <v>250</v>
+      </c>
+      <c r="C2" s="6">
+        <v>1.3114539999999999E-4</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="14">
+        <f>A2^2</f>
         <v>10000</v>
       </c>
-      <c r="B2" s="1">
+      <c r="F2" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="14"/>
+      <c r="H2" s="5">
+        <v>100</v>
+      </c>
+      <c r="I2" s="14">
+        <f>C2</f>
+        <v>1.3114539999999999E-4</v>
+      </c>
+      <c r="J2" s="5">
+        <f>C2</f>
+        <v>1.3114539999999999E-4</v>
+      </c>
+      <c r="K2" s="14">
+        <f>J2-I2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="8">
         <v>1000</v>
       </c>
-      <c r="C2" s="2">
-        <v>4.4468351999999997E-3</v>
-      </c>
+      <c r="B3" s="15">
+        <v>250</v>
+      </c>
+      <c r="C3" s="10">
+        <v>4.4442560000000002E-4</v>
+      </c>
+      <c r="D3" s="18">
+        <f>C3/C2</f>
+        <v>3.3888005221685247</v>
+      </c>
+      <c r="E3" s="15">
+        <f>A3^2</f>
+        <v>1000000</v>
+      </c>
+      <c r="F3" s="11">
+        <f>E3/E2</f>
+        <v>100</v>
+      </c>
+      <c r="G3" s="15"/>
+      <c r="H3" s="8">
+        <v>1000</v>
+      </c>
+      <c r="I3" s="15">
+        <f>(D3)*I2</f>
+        <v>4.4442560000000002E-4</v>
+      </c>
+      <c r="J3" s="8">
+        <f>(F3)*J2</f>
+        <v>1.3114539999999999E-2</v>
+      </c>
+      <c r="K3" s="15">
+        <f t="shared" ref="K3:K7" si="0">J3-I3</f>
+        <v>1.26701144E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="8">
+        <v>10000</v>
+      </c>
+      <c r="B4" s="15">
+        <v>250</v>
+      </c>
+      <c r="C4" s="10">
+        <v>4.2838947199999996E-3</v>
+      </c>
+      <c r="D4" s="18">
+        <f>C4/C3</f>
+        <v>9.6391718208852044</v>
+      </c>
+      <c r="E4" s="15">
+        <f>A4^2</f>
+        <v>100000000</v>
+      </c>
+      <c r="F4" s="11">
+        <f>E4/E3</f>
+        <v>100</v>
+      </c>
+      <c r="G4" s="15"/>
+      <c r="H4" s="8">
+        <v>10000</v>
+      </c>
+      <c r="I4" s="15">
+        <f>(D4)*I3</f>
+        <v>4.2838947199999996E-3</v>
+      </c>
+      <c r="J4" s="8">
+        <f>(F4)*J3</f>
+        <v>1.3114539999999999</v>
+      </c>
+      <c r="K4" s="15">
+        <f t="shared" si="0"/>
+        <v>1.30717010528</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="8">
+        <v>100000</v>
+      </c>
+      <c r="B5" s="15">
+        <v>250</v>
+      </c>
+      <c r="C5" s="10">
+        <v>3.947757348E-2</v>
+      </c>
+      <c r="D5" s="18">
+        <f>C5/C4</f>
+        <v>9.2153463285857793</v>
+      </c>
+      <c r="E5" s="15">
+        <f>A5^2</f>
+        <v>10000000000</v>
+      </c>
+      <c r="F5" s="11">
+        <f>E5/E4</f>
+        <v>100</v>
+      </c>
+      <c r="G5" s="15"/>
+      <c r="H5" s="8">
+        <v>100000</v>
+      </c>
+      <c r="I5" s="15">
+        <f>(D5)*I4</f>
+        <v>3.947757348E-2</v>
+      </c>
+      <c r="J5" s="8">
+        <f>(F5)*J4</f>
+        <v>131.1454</v>
+      </c>
+      <c r="K5" s="15">
+        <f t="shared" si="0"/>
+        <v>131.10592242651998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="8">
+        <v>1000000</v>
+      </c>
+      <c r="B6" s="15">
+        <v>250</v>
+      </c>
+      <c r="C6" s="10">
+        <v>0.38916964316000002</v>
+      </c>
+      <c r="D6" s="18">
+        <f>C6/C5</f>
+        <v>9.8579930034747427</v>
+      </c>
+      <c r="E6" s="15">
+        <f>A6^2</f>
+        <v>1000000000000</v>
+      </c>
+      <c r="F6" s="11">
+        <f>E6/E5</f>
+        <v>100</v>
+      </c>
+      <c r="G6" s="15"/>
+      <c r="H6" s="8">
+        <v>1000000</v>
+      </c>
+      <c r="I6" s="15">
+        <f>(D6)*I5</f>
+        <v>0.38916964316000008</v>
+      </c>
+      <c r="J6" s="8">
+        <f>(F6)*J5</f>
+        <v>13114.539999999999</v>
+      </c>
+      <c r="K6" s="15">
+        <f t="shared" si="0"/>
+        <v>13114.150830356839</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="12">
+        <v>10000000</v>
+      </c>
+      <c r="B7" s="16">
+        <v>250</v>
+      </c>
+      <c r="C7" s="2">
+        <v>4.6873352859599997</v>
+      </c>
+      <c r="D7" s="19">
+        <f>C7/C6</f>
+        <v>12.044452511505085</v>
+      </c>
+      <c r="E7" s="16">
+        <f>A7^2</f>
+        <v>100000000000000</v>
+      </c>
+      <c r="F7" s="13">
+        <f>E7/E6</f>
+        <v>100</v>
+      </c>
+      <c r="G7" s="16"/>
+      <c r="H7" s="12">
+        <v>10000000</v>
+      </c>
+      <c r="I7" s="16">
+        <f>(D7)*I6</f>
+        <v>4.6873352859600006</v>
+      </c>
+      <c r="J7" s="12">
+        <f>(F7)*J6</f>
+        <v>1311454</v>
+      </c>
+      <c r="K7" s="16">
+        <f t="shared" si="0"/>
+        <v>1311449.3126647139</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>